--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -611,6 +611,4256 @@
       <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>original_data_usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>icr-identify-age-related-conditions</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ICR - Identifying Age-Related Conditions</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Featured</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6430</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>56</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>No FE (overfitting); multi-label CV strategy; reweighting probabilities at output</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>NN</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>playground-series-s4e7</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Binary Classification of Insurance Cross Selling</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2234</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Feature store (12 versions); component models on feature subsets (previously insured, vehicle damage); feature importance via CatBoost single-fold</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, NN</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>playground-series-s5e3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Binary Prediction with a Rainfall Dataset</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4381</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>grouped</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>No FE; original data added as new columns via target mapping (merge_columns approach)</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>XGBoost, CatBoost, TabPFN, LogisticRegression, SVC, SVR</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>merge_columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>playground-series-s5e5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Predict Calorie Expenditure</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4316</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>hill_climbing</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>log1p transforms; product/division/sum/diff pairs; binned features (9 bins); groupby z-score features (26); residual modeling (NN on LR residuals, XGB on NN residuals); cuML TargetEncoder</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>XGBoost, CatBoost, NN, LinearRegression</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>playground-series-s5e12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Diabetes Prediction Challenge</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4206</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>post_cutoff</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Rank transformation; varied FE approaches across ~100 base models</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, NN, Ridge, AutoML</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Predicting Road Accident Risk</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4082</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Autoencoder latent features; genetic programming features (11 GP); XGBoost residual boosting; multiple feature type representations (categorical/numerical/mixed)</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>XGBoost, CatBoost, NN, Lasso, AutoGluon, Autoencoder</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Loan Approval Prediction</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3858</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Dual numeric+categorical feature representation; large max_bin values; original dataset included</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>LightGBM, XGBoost, CatBoost, NN</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>playground-series-s5e11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Predicting Loan Payback</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3724</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>hill_climbing</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Digit extraction from numericals; pairwise/triple/quadruple digit interactions + TE/CE; base feature pairs + TE/CE; quantile binning; categorical version of credit_score; TE with alternative targets</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, NN, LogisticRegression, RandomForest, ExtraTrees</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>playground-series-s4e1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Binary Classification with a Bank Churn Dataset</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3632</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Subset matching — all 1-10 element feature subsets checked against original dataset (~1000 binary indicators); CustomerId+Surname subset; post-processing probability shift</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>LightGBM, AutoGluon</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>AutoGluon</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>feature_lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>playground-series-s5e2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Backpack Prediction Challenge</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3393</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Groupby aggregations (mean/std/count/min/max/nunique/skew); groupby histogram bins; groupby quantiles; NaN base-2 encoding; numerical rounding/binning; digit extraction from floats; categorical column combinations (all pairs); division features (ratios of aggregated features)</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>merge_columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>playground-series-s5e8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Binary Classification with a Bank Dataset</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3365</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>TE/CE on feature bigrams (competition + original targets); products of numerical bigrams; cyclical features</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, NN, RandomForest</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>playground-series-s5e4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Predict Podcast Listening Time</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3310</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Target ratio transformation (target/Episode_Length); Episode_Length imputation via model; pseudo labeling (train+test); residual boosting (GBDT on Lasso/SVR/MLP residuals); 6000 features for linear models; diverse feature sets per model</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, NN, Lasso, SVR, KNN, RandomForest, AutoGluon</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>playground-series-s4e9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Regression of Used Car Prices</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3066</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>clip</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>CatBoost classifier OOF as feature for LGBM; SVR OOF as NN feature; median target encoding (leakfree per fold); rare category grouping; outlier price binning via IQR</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>LightGBM, CatBoost, SVR, NN, XGBoost, AutoGluon</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Regression with a Flood Prediction Dataset</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2788</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Row-wise statistics (sum/std/max); sorted features; count threshold features (nb_sup6/7/8); target encoding on row sum; target transformation (subtract feature mean x0.1); permutation + backward feature selection</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, AutoGluon</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>playground-series-s4e11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Exploring Mental Health Data</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2685</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, AutoGluon</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>AutoGluon</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>playground-series-s5e6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Predicting Optimal Fertilizers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2648</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>multiclass</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>hill_climbing</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>All pairs/triples/quadruples of 8 features (162 combos); TE of 162 combos x7 binary targets (2268 cols); TE using original dataset; residual boosting (XGB over LR base margin); pseudo labeling; repeated KFold seed averaging; retrain on 100% data</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, NN, LinearRegression, KNN</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>concat_rows, merge_columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>playground-series-s4e8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Binary Prediction of Poisonous Mushrooms</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2422</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Original dataset poisonous probability as engineered feature; confident disagreement overwriting (predictions &gt;0.99 threshold)</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>LightGBM, XGBoost, CatBoost, RandomForest, ExtraTrees, AutoGluon</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>playground-series-s4e12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Regression with an Insurance Dataset</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2390</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Label encoding; TE (mean/median/min/max/nunique) + CE per column; column combinations (2-6 way); treating numerics as categorical + TE/CE; Policy Start Date decomposition; GPU-accelerated search of 145K+ combinations -&gt; 170 kept</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>playground-series-s4e3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Steel Plate Defect Prediction</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2199</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>multiclass</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ratio features (length/thickness); range x area interaction; min-max normalized thickness feature; feature dropping via CV + feature importance + correlation</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, HistGB</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>playground-series-s3e24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Binary Prediction of Smoker Status using Bio-Signals</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1908</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Brute-force feature combinations (80-120 kept); permutation importance for feature pruning</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>LightGBM, XGBoost, CatBoost, RandomForest, LogisticRegression, TabNet, NN, GAM</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>playground-series-s3e23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Binary Classification with a Software Defects Dataset</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1702</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>hill_climbing</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Log transformation of all features (core improvement); PCA/t-SNE/clustering tried but failed</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>LightGBM, XGBoost, CatBoost, RandomForest, ExtraTrees, HistGB, LogisticRegression, NN</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>playground-series-s3e14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Regression with a Wild Blueberry Yield Dataset</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Post-processing: match test rows to original dataset by fruitset+fruitmass key -&gt; assign original yield values; automated matching script (2073 test samples x 776 unique yields)</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>feature_lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>playground-series-s3e26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Multi-Class Prediction of Cirrhosis Outcomes</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1661</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>multiclass</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>OHE</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Piecewise linear encoding (PLE) for continuous features; embedding layers for categorical features (edema, stage)</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, NN</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>playground-series-s3e16</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Regression with a Crab Age Dataset</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1429</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Domain features (meat yield/surface area/weight ratios/pseudo BMI/viscera ratio); log transform on weight; post-processing (round to nearest integer); feature subset selection (6-10 features per model)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, HistGB</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>playground-series-s3e17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Binary Classification of Machine Failures</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1502</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>None described — AutoML handles internally</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>AutoML</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>playground-series-s3e11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Regression with a Tabular Media Campaign Cost Dataset</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Feature subset selection across models; duplicate grouping (360K-&gt;3000 groups); log1p target transformation; store_sqft treated as categorical</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>LightGBM, XGBoost, CatBoost, RandomForest, ExtraTrees, NN</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>playground-series-s3e13</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Classification with a Tabular Vector Borne Disease Dataset</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>934</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>multiclass</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>LightGBM, NN, Autoencoder</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>playground-series-s3e5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ordinal Regression with a Tabular Wine Quality Dataset</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>901</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>multiclass</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>None — FE tried but worsened CV; post-processing with OptimizedRounder for ordinal class cutoffs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>not_used</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>playground-series-s3e10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Binary Classification with a Tabular Pulsar Dataset</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>807</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>XGBoost predictions as GAM input features; Lasso predictions as GAM input features; interaction terms in GAM</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>GAM, XGBoost, Lasso</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>GAM</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>playground-series-s3e9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Regression with a Tabular Concrete Strength Dataset</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>765</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Nonlinear features for linear regression (from partial dependence plots); feature selection by CV; target encoding of AgeInDays (treated as categorical)</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>LightGBM, GradientBoosting, RandomForest, LinearRegression</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>playground-series-s3e8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Regression with a Tabular Gemstone Price Dataset</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>734</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2023-04-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ordinal encoding of gemstone quality categoricals; aspect ratio features; carat x aspect ratio interaction; encoding methodology comparison via CV</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, Ridge, NN</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>playground-series-s3e6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Regression with a Tabular Paris Housing Price Dataset</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>703</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Permutation importance for feature selection (per model separately)</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>XGBoost, CatBoost, RandomForest, LightGBM</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>playground-series-s3e1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Regression with a Tabular California Housing Dataset</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>689</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Coordinate-based geographic features (from public notebook)</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, RandomForest, NN</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>playground-series-s3e7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Binary Classification with a Tabular Reservation Cancellation Dataset</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>678</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2023-04-30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>OHE</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>blending</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Categorical feature identification; OHE vs native encoding comparison; duplicate/leakage exploitation (opposite label assignment; predict 0.5 for test duplicates); adversarial validation to filter original dataset; removal of train duplicates with test counterparts</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>playground-series-s3e3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Binary Classification with a Tabular Employee Attrition Dataset</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>665</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2023-02-28</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Domain-driven risk flags (age&lt;34; hourly rate&lt;60; distance&gt;=20; tenure&lt;4 years; job hopper); composite AttritionRisk score; MonthlyIncome/Age ratio; AverageTenure (TotalWorkingYears/NumCompaniesWorked)</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>not_described</t>
         </is>
       </c>
     </row>

--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -67,13 +69,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AJ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -478,139 +481,179 @@
           <t>competition_ref</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>winner_1st</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>winner_2nd</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>winner_3rd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>is_monetized</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_teams</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>target_type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>n_features</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>pct_missing</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>feature_type_dominant</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>has_categorical</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>distribution_shift</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>finish_rank</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>writeup_detail</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>writeup_url</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>code_url</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>missing_data_strategy</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>encoding_strategy</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>outlier_treatment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>scaling</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>primary_model</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cv_strategy</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>rare_class_handling</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ensemble_method</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>fe_techniques</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>models_used</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>best_single_model</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hyperparameter_tuning</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>original_data_usage</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>dominant_base_model</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>n_rows</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>max_cardinality</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>metric</t>
         </is>
       </c>
     </row>
@@ -622,121 +665,158 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>room722</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Banana Overfit Capybaras</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>siguo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>ICR - Identifying Age-Related Conditions</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Featured</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>6430</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>56</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>57</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/icr-identify-age-related-conditions/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>No FE (overfitting); multi-label CV strategy; reweighting probabilities at output</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>NN</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>No FE (overfitting); multi-label CV strategy; reweighting probabilities at output</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>NN</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>NN</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>617</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Weighted Multiclass Loss</t>
         </is>
       </c>
     </row>
@@ -748,119 +828,163 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Cross Sellers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ujjwal Pandey</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tilii</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Binary Classification of Insurance Cross Selling</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>2234</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2024-07-31</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e7/writeups/cross-sellers-winning-approach-team-cross-sellers</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/ravi20076/playgrounds4e07-featurestore</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>stratified_kfold</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Feature store (12 versions); component models on feature subsets (previously insured, vehicle damage); feature importance via CatBoost single-fold</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, CatBoost, NN</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lightgbm, catboost, xgboost, neural_network (denselight, mlp, tab_resnet, tab_transformer, autoint)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>CatBoost</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>11504798</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -872,119 +996,158 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Guillaume HIMBERT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chris Deotte</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AndNov</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Binary Prediction with a Rainfall Dataset</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>4381</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e3/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>grouped</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>mean_blend</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>No FE; original data added as new columns via target mapping (merge_columns approach)</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>XGBoost, CatBoost, TabPFN, LogisticRegression, SVC, SVR</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>SVC</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>merge_columns</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>2190</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -996,115 +1159,163 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Chris Deotte</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mahog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>nice kazusan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Predict Calorie Expenditure</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>4316</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e5/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/cdeotte/gpu-hill-climbing-cv-0-05930</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>kfold</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>hill_climbing</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>log1p transforms; product/division/sum/diff pairs; binned features (9 bins); groupby z-score features (26); residual modeling (NN on LR residuals, XGB on NN residuals); cuML TargetEncoder</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>XGBoost, CatBoost, NN, LinearRegression</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>xgboost</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Mean Squared Log Error</t>
         </is>
       </c>
     </row>
@@ -1116,115 +1327,158 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>wind1234it</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>甜食爱好者</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Öinen Huuhkaja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Diabetes Prediction Challenge</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>4206</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e12/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/wind1234it/s5e12-1st-place-solution-hc-ridge</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>post_cutoff</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>stacking</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Rank transformation; varied FE approaches across ~100 base models</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>hill_climbing; stacking</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ratio features (medical domain pairs); polynomial features (sq; cb); target encoding; original data concat</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>XGBoost, LightGBM, CatBoost, NN, Ridge, AutoML</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -1236,115 +1490,158 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Tilii</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>steubk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Predicting Road Accident Risk</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>4082</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>13</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e10/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/tilii7/s5e10-genetic-programming-features</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>one_hot_encoding</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>stacking</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>hill_climbing; stacking</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Autoencoder latent features; genetic programming features (11 GP); XGBoost residual boosting; multiple feature type representations (categorical/numerical/mixed)</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>XGBoost, CatBoost, NN, Lasso, AutoGluon, Autoencoder</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>517754</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -1356,119 +1653,163 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Hardy Xu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OMID BAGHCHEH SARAEI</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>nadavcherry</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Loan Approval Prediction</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>3858</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>12</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
+      <c r="Q8" t="n">
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e10/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/omidbaghchehsaraei/ensemble-modeling-for-loan-approval</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>stacking</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Dual numeric+categorical feature representation; large max_bin values; original dataset included</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>LightGBM, XGBoost, CatBoost, NN</t>
+          <t>stratified_kfold</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>CatBoost</t>
+          <t>not_described</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>optuna</t>
+          <t>hill_climbing</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>original data concat; dual numeric+categorical representation</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>LightGBM; XGBoost; CatBoost; ExtraTrees; RandomForest; KNN; MLP</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>58645</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -1480,119 +1821,163 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Mahog</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AngelosMar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Öinen Huuhkaja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Predicting Loan Payback</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>3724</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2025-11-30</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e11/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/mahoganybuttstrings/pg-s5e11-xgb-cv-0-92818-pb-0-92923</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>target_encoding; count_encoding</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>hill_climbing</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>hill_climbing; stacking</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Digit extraction from numericals; pairwise/triple/quadruple digit interactions + TE/CE; base feature pairs + TE/CE; quantile binning; categorical version of credit_score; TE with alternative targets</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, CatBoost, NN, LogisticRegression, RandomForest, ExtraTrees</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>XGBoost; LightGBM; CatBoost; RealMLP; TabM; DANet; Resnet; LogisticRegression; RandomForest; ExtraTrees; FTTransformer; DeepFM; LNN; Trompt; Gandalf; Bartz</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>593994</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -1604,119 +1989,163 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Nikolay Slobodchuk</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lukaszl</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Iqbal Syah Akbar</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Binary Classification with a Bank Churn Dataset</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>3632</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2024-01-31</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>13</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e1/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/iqbalsyahakbar/ps4e1-3rd-place-solution</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Subset matching — all 1-10 element feature subsets checked against original dataset (~1000 binary indicators); CustomerId+Surname subset; post-processing probability shift</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>LightGBM, AutoGluon</t>
+          <t>stratified_kfold</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>AutoGluon</t>
+          <t>not_described</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>weighted_blend</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>feature_lookup</t>
+          <t>tfidf_svd, feature_creation, interaction_features, numeric_type_casting</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>logistic_regression, neural_network, xgboost, lightgbm, catboost</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>catboost</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>165034</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2797</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -1728,119 +2157,163 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Chris Deotte</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ravi Ramakrishnan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>automatylicza_knai</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Backpack Prediction Challenge</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>3393</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>ordinal</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e2/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/cdeotte/first-place-single-model-lb-38-81</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>target_encoding; label_encoding</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Groupby aggregations (mean/std/count/min/max/nunique/skew); groupby histogram bins; groupby quantiles; NaN base-2 encoding; numerical rounding/binning; digit extraction from floats; categorical column combinations (all pairs); division features (ratios of aggregated features)</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Groupby aggregations (mean/std/count/min/max/nunique/skew); groupby histogram bins; groupby quantiles; NaN base-2 encoding; numerical rounding/binning; digit extraction from floats; categorical column combinations (all pairs); division features (ratios of aggregated features)</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>merge_columns</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -1852,115 +2325,163 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Optimistix</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mahog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Succeeded. Resource recovered</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Binary Classification with a Bank Dataset</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>3365</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e8/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/mahoganybuttstrings/pg-s5e8-tabm-cv-0-976810-pb-0-97750</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>target_encoding; count_encoding</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>TE/CE on feature bigrams (competition + original targets); products of numerical bigrams; cyclical features</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, CatBoost, NN, RandomForest</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>tabm, xgboost, lightgbm, catboost, neural_network, random_forest, bart</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>tabm</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>750000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -1972,84 +2493,92 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Chris Deotte</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Farukcan Saglam</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Johannes Heller</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Predict Podcast Listening Time</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>3310</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e4/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/greysky/podcast-model-training</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ensemble</t>
+          <t>not_described</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>kfold</t>
+          <t>target_encoding</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2059,28 +2588,68 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>stacking</t>
+          <t>none</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Target ratio transformation (target/Episode_Length); Episode_Length imputation via model; pseudo labeling (train+test); residual boosting (GBDT on Lasso/SVR/MLP residuals); 6000 features for linear models; diverse feature sets per model</t>
+          <t>gbm</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>XGBoost, LightGBM, NN, Lasso, SVR, KNN, RandomForest, AutoGluon</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>target_encoding_pairs (1-6 way), interaction_features, rounding_features, te_descriptive_stats</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>lightgbm</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>lightgbm</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>750000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -2092,115 +2661,163 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Mart Preusse</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gerlando Re</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Optimistix</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Regression of Used Car Prices</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>3066</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>clip</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e9/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/martinapreusse/ps4e9-cat-svr-lgbm-nn-py</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>imputation</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>target_encoding; label_encoding</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>outlier_classification</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>kfold</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>rare_grouping</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>CatBoost classifier OOF as feature for LGBM; SVR OOF as NN feature; median target encoding (leakfree per fold); rare category grouping; outlier price binning via IQR</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>text_feature_extraction (horsepower/displacement from engine), mileage_binning, outlier_classification (IQR price_bin), target_encoding_median (leakfree per fold), catboost_oof_as_feature</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>LightGBM, CatBoost, SVR, NN, XGBoost, AutoGluon</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>optuna</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>188533</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1897</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -2212,115 +2829,158 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>aldparis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Peaky Blenders</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tilii</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Regression with a Flood Prediction Dataset</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>2788</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2024-05-31</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>21</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e5/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/adaubas/pss4e05-1st-place-solution-ensemble-with-ridge</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>kfold</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>stacking</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>repeated_stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weighted_blend</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Row-wise statistics (sum/std/max); sorted features; count threshold features (nb_sup6/7/8); target encoding on row sum; target transformation (subtract feature mean x0.1); permutation + backward feature selection</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>XGBoost, LightGBM, CatBoost, AutoGluon</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>optuna</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>1117957</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>R2 Score</t>
         </is>
       </c>
     </row>
@@ -2332,119 +2992,163 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Mahdi Ravaghi</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gougou1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Martynov Andrey</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Exploring Mental Health Data</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="H16" t="n">
         <v>2685</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>19</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e11/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/ravaghi/s04e11-mental-health-prediction-ensemble</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
+          <t>imputation</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>ordinal_encoding; one_hot_encoding</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, AutoGluon</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>xgboost, lightgbm, catboost, logistic_regression, gradient_boosting, adaboost, autogluon</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>AutoGluon</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>140700</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>422</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Accuracy Score</t>
         </is>
       </c>
     </row>
@@ -2456,115 +3160,153 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Chris Deotte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Masaya Kawamata</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mahog</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Predicting Optimal Fertilizers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="H17" t="n">
         <v>2648</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>multiclass</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e6/discussion?sortBy=voteCount</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>stratified_kfold</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>hill_climbing</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>All pairs/triples/quadruples of 8 features (162 combos); TE of 162 combos x7 binary targets (2268 cols); TE using original dataset; residual boosting (XGB over LR base margin); pseudo labeling; repeated KFold seed averaging; retrain on 100% data</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, CatBoost, NN, LinearRegression, KNN</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>xgboost, lightgbm, catboost, neural_network, linear_regression</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>concat_rows, merge_columns</t>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>concat_rows; merge_columns</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>750000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>MAP@{K}</t>
         </is>
       </c>
     </row>
@@ -2576,119 +3318,158 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Optimistix</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sujal Neupane</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AutoML Grandmasters</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Binary Prediction of Poisonous Mushrooms</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="H18" t="n">
         <v>2422</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2024-08-31</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>21</v>
+      </c>
+      <c r="L18" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e8/writeups/optimistix-1st-place-solution-72-oofs-a-whole-lott</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>stacking</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weighted_blend; hill_climbing; stacking</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Original dataset poisonous probability as engineered feature; confident disagreement overwriting (predictions &gt;0.99 threshold)</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>LightGBM, XGBoost, CatBoost, RandomForest, ExtraTrees, AutoGluon</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>lightgbm, xgboost, catboost, random_forest, extra_trees, autogluon</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>3116945</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>83</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Matthews Corrcoef</t>
         </is>
       </c>
     </row>
@@ -2700,119 +3481,163 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Chris Deotte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SCRIPTCHEF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Evgeny Nevodnich</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Regression with an Insurance Dataset</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="H19" t="n">
         <v>2390</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
         <v>3</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e12/writeups/chris-deotte-1st-place-single-model-feature-engine</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/cdeotte/first-place-single-model-cv-1-016-lb-1-016</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>imputation</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>target_encoding; label_encoding; count_encoding</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>kfold</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Label encoding; TE (mean/median/min/max/nunique) + CE per column; column combinations (2-6 way); treating numerics as categorical + TE/CE; Policy Start Date decomposition; GPU-accelerated search of 145K+ combinations -&gt; 170 kept</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>xgboost</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>xgboost</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>167381</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Logarithmic Error</t>
         </is>
       </c>
     </row>
@@ -2824,115 +3649,158 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>kailai</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Moonlit</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Samvel Kocharyan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Steel Plate Defect Prediction</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="H20" t="n">
         <v>2199</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>2024-03-31</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>multiclass</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>34</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
         <v>2</v>
       </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e3/writeups/moonlit-2nd-place-solution-oof-ensemble</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/yunqicao/2nd-place-solution-steel-plate-defect-prediction</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>drop</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>kfold</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weighted_blend</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Ratio features (length/thickness); range x area interaction; min-max normalized thickness feature; feature dropping via CV + feature importance + correlation</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, CatBoost, HistGB</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>xgboost, lightgbm, catboost, hist_gradient_boosting</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>optuna</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>19219</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Mean Columnwise Area Under Receiver Operating Characteristic Curve</t>
         </is>
       </c>
     </row>
@@ -2944,115 +3812,153 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>🇰🇷Pearl-Luck🇰🇷</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chan Lee</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ravi Ramakrishnan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Binary Prediction of Smoker Status using Bio-Signals</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="H21" t="n">
         <v>1908</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>2023-12-31</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>23</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M21" t="n">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
         <v>3</v>
       </c>
-      <c r="N21" t="n">
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e24/writeups/ravi-ramakrishnan-3-private-8-public-approach-simp</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>stratified_kfold</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weighted_blend; hill_climbing; stacking</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Brute-force feature combinations (80-120 kept); permutation importance for feature pruning</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>LightGBM, XGBoost, CatBoost, RandomForest, LogisticRegression, TabNet, NN, GAM</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>lightgbm, xgboost, catboost, random_forest, logistic_regression, tabnet, neural_network, gam</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>optuna</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>159256</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -3064,115 +3970,158 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>theod</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Oscar Aguilar</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>norm-usr</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Binary Classification with a Software Defects Dataset</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="H22" t="n">
         <v>1702</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>2023-11-30</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>22</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
         <v>2</v>
       </c>
-      <c r="N22" t="n">
+      <c r="Q22" t="n">
         <v>3</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e23/writeups/oscar-aguilar-2-solution-8-models-ensemble</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
+          <t>https://www.kaggle.com/code/oscarm524/ps-s3-ep23-eda-modeling-submission</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>log</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>hill_climbing</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>Log transformation of all features (core improvement); PCA/t-SNE/clustering tried but failed</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>LightGBM, XGBoost, CatBoost, RandomForest, ExtraTrees, HistGB, LogisticRegression, NN</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>lightgbm, xgboost, catboost, random_forest, extra_trees, histgb, logistic_regression, nn</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>101763</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -3184,115 +4133,158 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Sergey Saharovskiy</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>aci.patlican</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>hikahika</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Regression with a Wild Blueberry Yield Dataset</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="H23" t="n">
         <v>1875</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>17</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
         <v>2</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e14/writeups/sergey-saharovskiy-1-winning-solution</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/sergiosaharovskiy/ps-s3e14-2023-first-place-winning-solution</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>repeated_kfold</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>Post-processing: match test rows to original dataset by fruitset+fruitmass key -&gt; assign original yield values; automated matching script (2073 test samples x 776 unique yields)</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>feature_lookup</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>lightgbm</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>concat_rows; feature_lookup</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>15289</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Mean Absolute Error</t>
         </is>
       </c>
     </row>
@@ -3304,115 +4296,153 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>kailai</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hardy Xu</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fengqian</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Multi-Class Prediction of Cirrhosis Outcomes</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="H24" t="n">
         <v>1661</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>multiclass</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>19</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>OHE</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e26/writeups/hardy-xu-2nd-place-with-help-from-nns</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>one_hot_encoding</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>Piecewise linear encoding (PLE) for continuous features; embedding layers for categorical features (edema, stage)</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, NN</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>lightgbm, xgboost, nn</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>optuna</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>7905</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Log Loss</t>
         </is>
       </c>
     </row>
@@ -3424,115 +4454,158 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Epikt</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Emincan Yilmaz</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ravi Ramakrishnan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Regression with a Crab Age Dataset</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="H25" t="n">
         <v>1429</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>2023-08-31</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
         <v>3</v>
       </c>
-      <c r="N25" t="n">
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e16/writeups/ravi-ramakrishnan-3rd-private-6th-public-brute-for</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>log</t>
+          <t>https://www.kaggle.com/code/ravi20076/playgrounds3e16-eda-baseline</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>label_encoding</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>stratified_kfold</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>Domain features (meat yield/surface area/weight ratios/pseudo BMI/viscera ratio); log transform on weight; post-processing (round to nearest integer); feature subset selection (6-10 features per model)</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>XGBoost, LightGBM, CatBoost, HistGB</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>xgboost, lightgbm, catboost, gradient_boosting, histgb</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
         <is>
           <t>optuna</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>74051</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Mean Absolute Error</t>
         </is>
       </c>
     </row>
@@ -3544,115 +4617,153 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>[Deleted] 11d44875-64fa-4a34-b8ac-63c86281cafe</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Andrey K.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ISoft</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Binary Classification of Machine Failures</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="H26" t="n">
         <v>1502</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>2023-09-30</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="n">
+        <v>13</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
         <v>3</v>
       </c>
-      <c r="N26" t="n">
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e17/writeups/isoft-3rd-solution-based-on-90-multi-automl-soluti</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>None described — AutoML handles internally</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>AutoML</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>light_automl, h2o_automl, flaml, lazy_classifier</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>136429</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>9976</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
         </is>
       </c>
     </row>
@@ -3664,115 +4775,158 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>AmbrosM</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DJ_C</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Möbius</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Regression with a Tabular Media Campaign Cost Dataset</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="H27" t="n">
         <v>952</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>16</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
+      <c r="Q27" t="n">
         <v>3</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e11/writeups/ambrosm-1-a-zoo-of-models</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
+          <t>https://www.kaggle.com/code/ambrosm/pss3e11-zoo-of-models</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>target_encoding; one_hot_encoding</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
           <t>log</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weighted_blend</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>Feature subset selection across models; duplicate grouping (360K-&gt;3000 groups); log1p target transformation; store_sqft treated as categorical</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>LightGBM, XGBoost, CatBoost, RandomForest, ExtraTrees, NN</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>lightgbm, xgboost, catboost, random_forest, extra_trees, histgb, ridge, nn</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>360336</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Mean Squared Log Error</t>
         </is>
       </c>
     </row>
@@ -3784,115 +4938,153 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Umar</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>rjZhang97</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Unworried1686</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Classification with a Tabular Vector Borne Disease Dataset</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="H28" t="n">
         <v>934</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>2023-07-15</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>multiclass</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
+      <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
+          <t>https://www.kaggle.com/competitions/playground-series-s3e13/writeups/umar-surprisingly-1-public-lb-0-37196-private-lb-0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>mean_blend</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>LightGBM, NN, Autoencoder</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>lightgbm, nn, autoencoder</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>707</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>MAP@{K}</t>
         </is>
       </c>
     </row>
@@ -3904,119 +5096,163 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Heitor Rapela Medeiros</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NHopeT</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Gilles Vandewiele</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Ordinal Regression with a Tabular Wine Quality Dataset</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="H29" t="n">
         <v>901</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2023-03-31</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>multiclass</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>12</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="P29" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="n">
+      <c r="Q29" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e5/writeups/heitor-rapela-medeiros-1st-place-solution-single-m</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/rapela/tpss3e5-1st-place-solution-rapids-xgboost</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>None — FE tried but worsened CV; post-processing with OptimizedRounder for ordinal class cutoffs</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>stratified_kfold</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>None — FE tried but worsened CV; post-processing with OptimizedRounder for ordinal class cutoffs</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>optuna</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>not_used</t>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>2056</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Cohen Kappa Score</t>
         </is>
       </c>
     </row>
@@ -4028,119 +5264,163 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Piotr Szulc</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Patrick Blackwill</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>aldparis</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Binary Classification with a Tabular Pulsar Dataset</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="H30" t="n">
         <v>807</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>2023-05-31</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
+      <c r="Q30" t="n">
         <v>2</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e10/writeups/piotr-szulc-1st-place-solution</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/seascape/how-to-detect-pulsars-with-gam-1st-place</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>XGBoost predictions as GAM input features; Lasso predictions as GAM input features; interaction terms in GAM</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>GAM, XGBoost, Lasso</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>GAM</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>117564</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Log Loss</t>
         </is>
       </c>
     </row>
@@ -4152,115 +5432,158 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>AmbrosM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>songzijian</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lonan Syayf</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Regression with a Tabular Concrete Strength Dataset</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="H31" t="n">
         <v>765</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2023-05-15</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e9/writeups/ambrosm-1-solution-cross-validation-and-diversity-win</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/ambrosm/pss3e9-winning-model</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>kfold</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>repeated_kfold</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>mean_blend</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>Nonlinear features for linear regression (from partial dependence plots); feature selection by CV; target encoding of AgeInDays (treated as categorical)</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>LightGBM, GradientBoosting, RandomForest, LinearRegression</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>LightGBM, XGBoost, CatBoost, GradientBoostingRegressor, HistGradientBoostingRegressor, RandomForest, Ridge</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>5407</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -4272,115 +5595,153 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Thierry Neusius</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Craig Thomas</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tevfik Erkut</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Regression with a Tabular Gemstone Price Dataset</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="H32" t="n">
         <v>734</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>2023-04-30</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" t="n">
+      <c r="Q32" t="n">
         <v>2</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>ordinal</t>
-        </is>
-      </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e8/writeups/craig-thomas-2nd-place-solution</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
+          <t>imputation</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>ordinal_encoding</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>kfold</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>Ordinal encoding of gemstone quality categoricals; aspect ratio features; carat x aspect ratio interaction; encoding methodology comparison via CV</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>XGBoost, LightGBM, CatBoost, Ridge, NN</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>random_search</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>193573</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -4392,115 +5753,158 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>Sujith K Mandala</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JohnG29</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Viktor Taran</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Regression with a Tabular Paris Housing Price Dataset</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="H33" t="n">
         <v>703</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>2023-04-15</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="n">
+        <v>17</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" t="n">
+      <c r="Q33" t="n">
         <v>2</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e6/writeups/viktor-taran-3rd-place</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/viktortaran/ps-s-3-e-6</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
+          <t>imputation</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>one_hot_encoding</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>kfold</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>repeated_kfold</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>Permutation importance for feature selection (per model separately)</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>XGBoost, CatBoost, RandomForest, LightGBM</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>22730</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -4512,115 +5916,153 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Kirderf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jcerpent</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Regression with a Tabular California Housing Dataset</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="H34" t="n">
         <v>689</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2023-01-31</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>regression</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="n">
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e1/writeups/kirderf-that-was-a-surprise-here-is-the-1st-place-</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>kfold</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>repeated_kfold</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>stacking</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>Coordinate-based geographic features (from public notebook)</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>XGBoost, LightGBM, CatBoost, RandomForest, NN</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>37137</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
         </is>
       </c>
     </row>
@@ -4632,115 +6074,153 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Hardy Xu</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jose Cáliz</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Craig Thomas</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Binary Classification with a Tabular Reservation Cancellation Dataset</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="H35" t="n">
         <v>678</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>2023-04-30</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>18</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="N35" t="n">
+      <c r="Q35" t="n">
         <v>2</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>OHE</t>
-        </is>
-      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e7/writeups/hardy-xu-1st-place-solution</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>one_hot_encoding</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>stratified_kfold</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>blending</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>repeated_stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>mean_blend</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>Categorical feature identification; OHE vs native encoding comparison; duplicate/leakage exploitation (opposite label assignment; predict 0.5 for test duplicates); adversarial validation to filter original dataset; removal of train duplicates with test counterparts</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>XGBoost, LightGBM</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH35" t="n">
+        <v>42100</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>Area Under Receiver Operating Characteristic Curve</t>
         </is>
       </c>
     </row>
@@ -4752,115 +6232,1786 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Bill Cruise</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Prasad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Cup of Dim</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Binary Classification with a Tabular Employee Attrition Dataset</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Playground</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="H36" t="n">
         <v>665</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>2023-02-28</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="n">
+        <v>34</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
         <v>1</v>
       </c>
-      <c r="N36" t="n">
+      <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/competitions/playground-series-s3e3/writeups/bill-cruise-1st-place-that-was-unexpected</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>https://www.kaggle.com/code/bcruise/starting-strong-xgboost-lightgbm-catboost</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>ordinal_encoding</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
           <t>ensemble</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weighted_blend</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>Domain-driven risk flags (age&lt;34; hourly rate&lt;60; distance&gt;=20; tenure&lt;4 years; job hopper); composite AttritionRisk score; MonthlyIncome/Age ratio; AverageTenure (TotalWorkingYears/NumCompaniesWorked)</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>XGBoost, LightGBM, CatBoost</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>not_described</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>not_described</t>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH36" t="n">
+        <v>1677</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>Area Under Receiver Operating Characteristic Curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>playground-series-s5e7</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rapfff</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Irfan Ahmad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Resmont</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Predict the Introverts from the Extroverts</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4329</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s5e7/discussion?sortBy=voteCount</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/irfanahmad1/introverts-and-extroverts-0-974-competetion-win</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>fill_missing_category</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>label_encoding</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weighted_blend</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>original data merge as new feature (match_p)</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>catboost; xgboost; lightgbm</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>catboost</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH37" t="n">
+        <v>18524</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>Accuracy Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>playground-series-s4e4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Johannes Heller</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lennart Purucker</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LuminousC</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Regression with an Abalone Dataset</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2606</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s4e4/writeups/johannes-heller-1st-place-solution-for-the-regress</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/stopwhispering/abalone-feature-engineering-preprocessor</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>one_hot_encoding</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>ensemble</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weighted_blend</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>automated_fe (OpenFE), feature_selection (sequential)</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>lightgbm, xgboost, catboost, hist_gradient_boosting, random_forest, autogluon</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>autogluon</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>bayesian</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>concat_rows</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH38" t="n">
+        <v>90615</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Mean Squared Log Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>not described</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>not described</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>olliekemp</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Binary Classification with a Tabular Credit Card Fraud Dataset</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>641</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>44956</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>30</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>not described</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/olliekemp/3rd-place-solution-ensemble-catboost</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>undersample</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>mean_blend</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>catboost</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>catboost</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH39" t="n">
+        <v>219129</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Area Under Receiver Operating Characteristic Curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-feb-2022</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ambrosm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jwallib</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Ozzy</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Feb 2022</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1255</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>44620</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>multiclass</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>286</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-feb-2022/writeups/ambrosm-1-solution-exploiting-the-flawed-random-ge</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/ambrosm/tpsfeb22-exploiting-the-flawed-random-generation</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Custom reverse-transformation of decamer counts to 100-dimensional random index space for Manhattan distance matching of train/test pairs sharing generation seed</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>RadiusNeighborsClassifier</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>RadiusNeighborsClassifier</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="AH40" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Categorization Accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-may-2022</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>The Team</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Joe Cooper</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Outatime</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - May 2022</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>44712</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>31</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-may-2022/writeups/the-team-1-solution-a-two-branch-network</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/pourchot/tpsmay22-keras-test-tuned</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>ordinal_encoding</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>mean_blend</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Xgbfir interaction graph analysis identifying two disconnected feature components; two-branch NN architecture restricting interactions to graph components; unique_characters feature; pairwise interaction features (i_02_21, i_05_22, i_00_01_26)</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Keras NN, LightGBM</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Keras NN</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH41" t="n">
+        <v>900000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>741354</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Area Under Receiver Operating Characteristic Curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-jun-2022</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sebastianvangerwen</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>arturra</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Patrick Chan</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Jun 2022</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>44742</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>81</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-jun-2022/writeups/sebastian-van-gerwen-1-solution-denoising-autoenco</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/sebastianvangerwen/1st-place-solution-tps-jun-denoising-ae</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>imputation</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>mean_blend</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Feature-wise linear embeddings of values and null mask with additive fusion; conditional ensemble by F4 null count (single-null rows predicted separately); mean imputation for F1 and F3 groups</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>DAE MLP (PyTorch, TensorFlow)</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>DAE MLP (TensorFlow)</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH42" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>playground-series-s6e1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>mahoganybuttstrings</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>tilii7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Funguscakehead</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Predicting Student Test Scores</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>46053</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>regression</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>11</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e1/writeups/1st-place-ive-ran-out-of-catchy-phrases-v</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/mahoganybuttstrings/pg-s6e1-ridge-ensemble-cv-8-56634-lb-8-57273</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>kfold</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Cyclical feature encoding; formula-based score feature from public discussion; categorical copy of each numeric feature for TE; digit features; TE (mean/std/skew) of feature and digit combinations; ordinal mapping of categorical features (GBDT set); Isotonic Regression post-processing</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>RealMLP, XGBoost, TabM, CatBoost, DeepTables, LightGBM, Keras MLP, ResNet, FTTransformer, FFM</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>RealMLP</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>random_search</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH43" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>masayakawamata</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Akiyoshi Kinoshita</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sa beyler turk warmi</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Predicting Heart Disease</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>46081</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>13</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e2/writeups/1st-place-solution-diversity-selection-and-t</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/masayakawamata/s6e2-single-realmlp</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Quantile and equal-width binning; digit features; all features treated as categorical; within-fold target encoding (cuml TargetEncoder, 5-fold, smooth=10); genetic programming (gplearn) nonlinear features; original dataset target statistics (mean, smoothed mean, WoE, entropy) as external TE; DVAE latent representations for diversity; knowledge distillation (soft labels = 0.5 * hard labels + 0.5 * teacher RealMLP OOF)</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, RealMLP, RGF, TabICL, AutoGluon</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>RealMLP</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH44" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Optimistix</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>include4eto</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Predict Customer Churn</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>19</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e3/writeups/1st-place-gpt5-4-gemini3-1-claudeopus4-6-kgm</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/cdeotte/1st-place-nvidia-cuml-logistic-regression</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Snap features (nearest original IBM value mapping); decimal digit extraction; nested/leak-free target encoding on all 16 categorical columns; bigrams, trigrams, binned numerics; arithmetic interactions (TC_deviation, MC-to-TC ratio); multi-scale binning (up to 5000 quantile bins); categorical cross-features; frequency/count encoding; service count aggregations; original IBM cKDTree nearest-neighbor lookup; radix interaction features; synthetic artifact detection (Benford's Law deviation, TF-IDF on numeric strings, fractional fingerprints); PCA/GRP projection on original IBM data; cyclical tenure features</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, YDF, cuML RF, Logistic Regression, Embedding MLP, RealMLP, TabM, TabICL, FT-Transformer, TabTransformer, GraphSAGE GNN, GANDALF, ResNet, FFM, FM, DeepFM, DCN, NAM, SAINT, SNN, IFAN, RFF, Cox regression, Liquid NN, DAE, TabNet, Trompt, TabPFN, VSN</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>TabM</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="AH45" t="n">
+        <v>594194</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>playground-series-s6e4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>kirill0212</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>nikita7364777</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Predicting Irrigation Need</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>multiclass</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>19</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e4/writeups/1st-place-one-vs-rest-approach</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/kirill0212/ps6e4-ensemble-cv-0-98155</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>target_encoding</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>stratified_kfold</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Digit features (individual digits at integer and decimal positions for all numeric columns); magnitude-based rounding of numerics; frequency encoding of categoricals and digit columns (rare categories mapped to default bucket); pairwise interaction cross-features (string concatenation of column pairs, filtered by key columns); target encoding (sklearn TargetEncoder)</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, RealMLP, TabM, Logistic Regression, HistGradientBoosting, YDF, GNN, Transformer</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="AH46" t="n">
+        <v>630000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy Score</t>
         </is>
       </c>
     </row>

--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -738,14 +738,19 @@
           <t>https://www.kaggle.com/competitions/icr-identify-age-related-conditions/discussion?sortBy=voteCount</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/room722/icr-adv-model</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>imputation</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>label_encoding</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -765,7 +770,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>repeated_kfold</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -775,7 +780,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>mean_blend</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -800,7 +805,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1069,6 +1074,11 @@
           <t>https://www.kaggle.com/competitions/playground-series-s5e3/discussion?sortBy=voteCount</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/cdeotte/rapids-svc-w-feature-engineering-lb-0-856</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>not_described</t>
@@ -1076,7 +1086,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1086,7 +1096,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1111,7 +1121,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>No FE; original data added as new columns via target mapping (merge_columns approach)</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1131,7 +1141,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>merge_columns</t>
+          <t>concat_rows;merge_columns</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -3235,7 +3245,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3260,7 +3270,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>stratified_kfold</t>
+          <t>repeated_stratified_kfold</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -3290,7 +3300,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>concat_rows; merge_columns</t>
+          <t>concat_rows;merge_columns</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -3887,7 +3897,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3937,7 +3947,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>optuna</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -4371,12 +4381,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>one_hot_encoding</t>
+          <t>not_described</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -4411,7 +4421,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Piecewise linear encoding (PLE) for continuous features; embedding layers for categorical features (edema, stage)</t>
+          <t>Piecewise linear encoding (PLE) for continuous features; embedding layers for categorical features (edema, stage); value rounding for GBT features</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -5666,6 +5676,11 @@
       <c r="R32" t="inlineStr">
         <is>
           <t>https://www.kaggle.com/competitions/playground-series-s3e8/writeups/craig-thomas-2nd-place-solution</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/code/craigmthomas/play-s3e8-eda-models</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">

--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1221,10 +1221,8 @@
           <t>numeric</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+      <c r="N5" t="b">
+        <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1580,7 +1578,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -2415,7 +2413,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2776,7 +2774,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>stratified_kfold</t>
+          <t>kfold</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2919,12 +2917,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>target_encoding</t>
+          <t>not_described</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -4060,7 +4058,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -4223,7 +4221,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -4676,7 +4674,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4702,7 +4700,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4932,7 +4930,7 @@
         <v>360336</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -5023,7 +5021,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -5088,9 +5086,6 @@
       </c>
       <c r="AH28" t="n">
         <v>707</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>11</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -5527,7 +5522,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>target_encoding</t>
+          <t>not_described</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -5685,7 +5680,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>imputation</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -5817,13 +5812,11 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -5848,7 +5841,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>imputation</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5913,9 +5906,6 @@
       </c>
       <c r="AH33" t="n">
         <v>22730</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -6230,9 +6220,6 @@
       <c r="AH35" t="n">
         <v>42100</v>
       </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
           <t>Area Under Receiver Operating Characteristic Curve</t>
@@ -6342,7 +6329,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>not_described</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -7145,7 +7132,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -7467,7 +7454,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -7628,7 +7615,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -7789,7 +7776,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -7950,7 +7937,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">

--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>kfold</t>
+          <t>stratified_kfold</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>not_described</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">

--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -5907,6 +5907,9 @@
       <c r="AH33" t="n">
         <v>22730</v>
       </c>
+      <c r="AI33" t="n">
+        <v>2</v>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>Root Mean Squared Error</t>

--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Competition Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Codebook" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Example (icr)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Paradigm &amp; Attribution" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +37,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +61,12 @@
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
+        <bgColor rgb="00DDDDDD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -69,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -77,6 +88,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8031,7 +8052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8335,6 +8356,193 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>not_used | concat_rows | merge_columns | fold_addition | not_described</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>--- Pass 2 (Paradigm &amp; Attribution sheet) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>paradigm</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>ensemble-stacking | single-model-FE | lookup-exploit | problem-fit-NN | community-template-tweak | mixed. Primary winning paradigm per per-writeup re-evaluation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>lookup_exploit_subtype</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>identity | inversion | distance-via-generator-flaw | exact-solution-feature | none. Only meaningful when paradigm = lookup-exploit; otherwise 'none'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>lookup_material_present</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE. TRUE if lookup-able material (exact-match, snap, KDTree, original target lookup, etc.) appeared anywhere in the solution, independent of primary paradigm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>origination_score</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>0-3 ordinal. 0=pure fork; 1=fork+small tweak; 2=significant original work on top of community foundation; 3=mostly original (pipeline+FE+models+ensemble all from winner).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cited_community_members</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Semicolon-separated Kaggle handles named in the writeup as technique/notebook/discussion sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>n_cited_members</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Count derived from cited_community_members.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>forked_from_public_notebook</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE. TRUE if the winning pipeline is built on a single forked public notebook as its base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>academic_papers_cited</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Semicolon-separated short labels (e.g. 'TFT (1912.09363)', 'PLE (2203.05556)').</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>uses_canonized_technique</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Semicolon-separated from {HC, brute-force-FE, Ridge-as-stacker, RAPIDS-XGB, AG-as-ensembler, target-encoding-stack, LAD-as-stacker, original-as-columns, MLP-stacker, DAE-as-base-encoder, pseudo-labeling, adversarial-validation}. Excluded: Optuna, OOF-stacking-generic, GroupKFold, standard model families.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>author_surprise_flag</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE. TRUE if writeup contains explicit 'didn't expect / how on earth / unexpected' framing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>author_recurring_in_set</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE. TRUE if author appears in &gt;1 row of this set (winner or cited source).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>author_appearance_count</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Total appearances of author across set (wins + citations).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>notable_commenters</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Semicolon-separated handles for commenters who are EITHER a Kaggle Grandmaster OR appear elsewhere in our set as winner/cited-source/recurring-author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>winner_unique_edge</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>One-line (&lt;=200 chars) description of the single thing distinguishing the winner from the public template / runner-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>reeval_doc</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Relative path to per-writeup re-evaluation doc.</t>
         </is>
       </c>
     </row>
@@ -8596,4 +8804,3602 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>competition_ref</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>finish_rank</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>author</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>paradigm</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>lookup_exploit_subtype</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>lookup_material_present</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>origination_score</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>cited_community_members</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>n_cited_members</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>forked_from_public_notebook</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>academic_papers_cited</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>uses_canonized_technique</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>author_surprise_flag</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>author_recurring_in_set</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>author_appearance_count</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>notable_commenters</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>winner_unique_edge</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>reeval_doc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>icr-identify-age-related-conditions</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>room722</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>problem-fit-NN</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>SAMUEL/muelsamu</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>TFT (1912.09363)</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;cpmpml;ravi20076</t>
+        </is>
+      </c>
+      <c r="Q2" s="8" t="inlineStr">
+        <is>
+          <t>NN-only at 617 rows via Variable Selection Network + dropout 0.75 + 10x10-30 repeated CV + multi-label CV + probability reweighting</t>
+        </is>
+      </c>
+      <c r="R2" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/icr_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e7</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>ravi20076+arunklenin (Cross Sellers)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>rzatemizel;uryednap;tilii7;optimistix</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>brute-force-FE;target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" s="8" t="inlineStr">
+        <is>
+          <t>tilii7;optimistix</t>
+        </is>
+      </c>
+      <c r="Q3" s="8" t="inlineStr">
+        <is>
+          <t>3-stage stacking with XGB final stacker; 78 weak learners; 12-version feature store; component models on data subsets; target reversal post-processing</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e7_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e3</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>RAPIDS-XGB;original-as-columns</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>Tiny-data playbook: no FE (curse of dimensionality), equal-weight mean blend of 3 models (XGB+TabPFN+RAPIDS SVC poly), Group K Fold by year</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e3_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e5</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>HC;RAPIDS-XGB;target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>mahog</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>GPU Hill Climbing canonization here; 7-model HC ensemble; residual modeling chain (LR-&gt;NN-&gt;XGB); groupby z-score features (26)</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e12</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>wind1234it</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>masayakawamata;daylighth;laureanoarcanio;tilii7;mikhailnaumov;siukeitin</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>HC;Ridge-as-stacker;original-as-columns</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>masayakawamata;tilii7</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>Post-cutoff CV (cutoff_id=678260) + HC with negative weights + Ridge stacker on rank-transformed top-36; ~100 base OOFs; anti-greedy submission</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e12_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>tilii7</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>masayakawamata;cdeotte;siukeitin;optimistix;mikhailnaumov;mahoganybuttstrings</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>HC;MLP-stacker;DAE-as-base-encoder</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;masayakawamata</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>11 genetic programming features added at ENSEMBLE stage (not base); Lasso used to reverse-engineer generator formula; Keras NN + CatBoost intermediate stackers</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e10</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>omidbaghchehsaraei</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>paddykb;siukeitin</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr"/>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>ravaghi;siukeitin</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>HC (hillclimbers library) over 21-24 models including paddykb's all-as-categorical port; anti-greedy submission (lower public LB, higher CV)</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e10_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e11</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>mahoganybuttstrings</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>masayakawamata;cdeotte;yekenot;yeoyunsianggeremie;jklol86;mikhailnaumov</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>HC;Ridge-as-stacker;target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;tilii7</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>Diversity-without-tuning: 23 model families with default HP + digit interaction combinatorics + TE with alternative targets (employment_status, debt_to_income)</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e1</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>iqbalsyahakbar</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>arunklenin;aspillai;paddykb</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr"/>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Ridge-as-stacker;target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>paddykb;aspillai</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>TF-IDF+SVD on text-like Surname then encode SVD components via CatBoost (double-layer FE); 30-fold CV for submission; CatBoost-encoder order-sensitivity</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e1_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e2</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>single-model-FE</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>jordanbarker</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>brute-force-FE;target-encoding-stack;RAPIDS-XGB;original-as-columns</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P11" s="8" t="inlineStr"/>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>Single XGB with 500 engineered features on 4M rows; histogram-binned groupby aggs (cdeotte invention); NaN base-2 encoding; nested-fold target-aware FE</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e8</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>mahoganybuttstrings</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;omidbaghchehsaraei;yekenot;itasps;siukeitin;tilii7</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr"/>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>HC;target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;tilii7</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>CatBoost as final stacker (beat Ridge by 0.00010 on private) in head-to-head 4-stacker test; 13 model architectures; TE on bigrams using comp + original targets</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e8_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e4</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>greysky</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>single-model-FE</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>Single LightGBM minimalist: 1552 features via 6-way TE combinatorics + descriptive stats; no CV, no ensemble, no HP tuning; Kaggle parallel-notebook experimentation</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e4_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e9</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>martinapreusse</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>yekenot;siukeitin;tilii7;roberthatch;noodl35;cdeotte</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr"/>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>MLP-stacker;Ridge-as-stacker</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>Last-day fork of yekenot's DeepTables NN starter + added 4 OOFs as features = NN-as-stacker won; outlier classification via IQR; median TE</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e9_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e5</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>adaubas (aldparis)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>mfmfmf3;igorvolianiuk;siukeitin;act18l;ambrosm;tilii7</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Ridge-as-stacker</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>innixma;tilii7;ambrosm</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>EDA-driven discovery: dataset is Poisson sum -&gt; row-wise stats FE; Ridge with negative weights (positive=False); only 2 submissions in 13 days (trust-CV)</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e11</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>ravaghi</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>optimistix;tilii7</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr"/>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>AG-as-ensembler</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>optimistix;tilii7</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>AutoGluon as final stacker (chosen over HC/Ridge/LR head-to-head); 24 models selected from 69; 4 data pipelines for diversity; anti-greedy submission</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e6</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>bizen250;ayushchandramaurya;elainedazzio;ricopue</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr"/>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>HC;target-encoding-stack;RAPIDS-XGB;original-as-columns;pseudo-labeling</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>mahog</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>Original-as-columns + cuDF TE at scale: 162 combos x 7 binary targets x 2 datasets = 2268 features; boosting over LR residuals; multi-seed averaging tuned to MAP@K</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e6_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e8</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>optimistix</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>exact-solution-feature</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>ambrosm;siukeitin;nischaydnk;gauravduttakiit;rzatemizel;ravaghi;oscarm524;ravi20076;tilii7;roberthatch;omidbaghchehsaraei;trupologhelper;arunklenin;carlmcbrideellis</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr"/>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>HC;AG-as-ensembler;Ridge-as-stacker</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>ravaghi;tilii7;ravi20076</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>Confident-disagreement-overwriting (&gt;0.99 threshold inserts) + 72 OOFs into AutoGluon-as-ensembler; three independent stacker paths converged at 0.98535</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e8_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e12</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>single-model-FE</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>brute-force-FE;target-encoding-stack;RAPIDS-XGB</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" s="8" t="inlineStr"/>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>GPU brute-force search of 145K+ categorical combinations -&gt; kept 170 that moved CV; explicit FE-effectiveness conditioning as strategy axis</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e12_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e3</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>yunqicao (Moonlit)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>community-template-tweak</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>noepinefrin;arunklenin;cyrilbourgeois;thomasmeiner;ankurgarg04;lucamassaron;arnogils</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr"/>
+      <c r="L20" s="8" t="inlineStr"/>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>arunklenin</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>Fork-heavy first-time competitor: 3 OOF ensembles (1 own + 2 public-notebook replications) + Nelder-Mead weights; public-notebook blend alone scores top-10</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e3_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e24</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>ravi20076</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>arunklenin;cv13j0;oscarm524;paddykb</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>brute-force-FE</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>paddykb;oscarm524</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>Brute-force FE search at Dec 2023 (predates cdeotte by 12 months, sourced from arunklenin); 8 model families incl TabNet+GAM; 10x1 vs 10x3 CV comparison</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e24_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e23</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>oscarm524</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>ambrosm;sauravpandey11</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr"/>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>ambrosm</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>HC ensemble of 8 models at Nov 2023 (predates cdeotte canonization by 18 months); log-transform on all features; Nystrom LogisticRegression</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e23_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e14</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>sergiosaharovskiy</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>lookup-exploit</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>zhukovoleksiy;paddykb;yzokulu;tetsutani;adaubas;mattop</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>LAD-as-stacker</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>adaubas;paddykb</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>Match test rows to original dataset by (fruitset, fruitmass) keys; assign exact original yield values (776 unique yields, 2073 test rows); largest 1-2 gap (0.657 MAE)</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e14_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e26</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>hardyxu52</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>PLE (2203.05556)</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>MLP-stacker</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" s="8" t="inlineStr"/>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>PLE for continuous features in NN; NN-as-final-stacker with per-class probability weights + cross-prediction weight calculation; 10 Optuna sets averaged per GBDT</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e26_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e16</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>ravi20076</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>pandeyg0811;inversion</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr"/>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>LAD-as-stacker</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P25" s="8" t="inlineStr"/>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>Generator-driven data augmentation (run official generator notebook with varied params); domain features (meat yield, pseudo BMI); feature-subset diversity per model</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e16_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e17</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>mathurinache (ISoft)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr"/>
+      <c r="L26" s="8" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="8" t="inlineStr"/>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>Pure-AutoML stack-of-stacks: 5 AutoML frameworks (Light AutoML, H2O, FLAML, Lazy Classifier, proprietary Statmining) ensembled; 6h on 4 cores 8GB; 10% public ports</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e17_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e11</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>ambrosm</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>Ridge-as-stacker;target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>sergiosaharovskiy</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>Earliest Ridge-as-stacker (Jun 2023); 18-model Zoo + Ridge weights; duplicate-grouping (360K-&gt;3K); PDP-based numerical-as-categorical detection (store_sqft)</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e13</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>mufathurrohman (Umar)</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>belati;mpwolke</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr"/>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>DAE-as-base-encoder</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="8" t="inlineStr"/>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>First-time competitor: 3-model mean-blend (LGBM + NN + frozen-encoder autoencoder-classifier) at 707 rows; default HP; cites 7-yr-old Porto Seguro autoencoder thread</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e13_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e5</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>rapela (Heitor)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>single-model-FE</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>paddykb;abhishek;carlmcbrideellis</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>RAPIDS-XGB</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>paddykb</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>Earliest single-model winner (Mar 2023): single RAPIDS XGBoost + OptimizedRounder (paddykb) + Optuna + 10-fold CV; chose NOT to use original (CV-driven)</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e10</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>seascape</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>single-model-FE</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>paddykb;adaubas</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>GAM as PRIMARY model (R .Rmd); XGB+Lasso predictions DEMOTED to input features for GAM; anti-boosting philosophy; reversed stacker hierarchy</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e9</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>ambrosm</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P31" s="8" t="inlineStr"/>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>First explicit anti-Optuna stance (manual HP &gt; Optuna); 7-model zoo + mean blend; quantitative trust-CV argument (5407 train vs 721 public LB = coin flip); PDP-based AgeInDays-as-categorical</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e9_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e8</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>craigmthomas</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>Ridge-as-stacker</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="8" t="inlineStr"/>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>Custom AutoML-like framework: 1,816 total models (1709 L1 + 105 L2 + Ridge stacker); threshold-based first-level selection; lookup-exploit TESTED and rejected (overfit public LB)</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e8_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e6</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>viktortaran</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="8" t="inlineStr"/>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>4-GBDT stack with LGBM as metamodel (tree-based stacker, counter to Ridge dominance); permutation importance per model; repeated KFold (5x10)</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e6_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e1</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>kirderf</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>dmitryuarov</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>AutoGluon (2003.06505)</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>AG-as-ensembler</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>innixma</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>Earliest AutoGluon-handles-everything win (Jan 2023); ported dmitryuarov's coordinate-based geo FE + AutoGluon = win; author explicit 'pure AutoML wouldn't have won'</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e1_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e7</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>hardyxu52</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>lookup-exploit</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>inversion</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>siukeitin</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>adversarial-validation</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>siukeitin</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>Opposite-label assignment exploit: 716 test rows had train twins with opposite labels; assigned opposite = +0.014 LB; siukeitin's 'predict 0.5 for test duplicates'</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e7_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e3</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>bcruise (Bill Cruise)</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>community-template-tweak</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>khawajaabaidullah</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr"/>
+      <c r="L36" s="8" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>Forked khawajaabaidullah's 3-GBDT notebook and added 7 domain-driven HR risk-flag features (Age&lt;34, JobHopper, AttritionRisk composite); win was the FE addition</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e3_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s5e7</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>irfanahmad1</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>lookup-exploit</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>exact-solution-feature</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="8" t="inlineStr"/>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>match_p trick: exact-row-join with public original on 7-feature tuple = match_p feature; 5 GBDT variants + Optuna negative-weight blend with threshold tuning</t>
+        </is>
+      </c>
+      <c r="R37" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e7_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s4e4</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>stopwhispering</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>endofnight17j03;inagana;siukeitin</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>OpenFE (Zhang 2022)</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>adversarial-validation</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" s="8" t="inlineStr"/>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>OpenFE academic tool for automated FE + SFS per model family + 49-model Nelder-Mead with negative coefficients (sum=0.997); anti-NN-for-tabular stance; MLOps</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e4_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>olliekemp</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>single-model-FE</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr"/>
+      <c r="L39" s="8" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" s="8" t="inlineStr"/>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>Custom CatTune class jointly tunes model params + sampling rate + class weights; 500-CatBoost random-jump pseudo-ensemble via Gaussian HP perturbation; aggregate stats over V cols</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e4_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-feb-2022</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>ambrosm</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>lookup-exploit</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>distance-via-generator-flaw</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>siukeitin</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Knuth AOCP Vol2</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>siukeitin</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>Reverse-engineered np.random.RandomState.choice flaw at source-code level (Knuth Alg K); reverse-transform 286 decamer counts -&gt; 100-element sequence; RadiusNeighborsClassifier wins (single model)</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_feb_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-may-2022</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>ambrosm+pourchot (The Team)</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>problem-fit-NN</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>sudalairajkumar (SRK);cabaxiom;wti200;pourchot</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr"/>
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>sudalairajkumar (SRK)</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>Architecture-from-data-structure: xgbfir interaction graph has 2 disconnected components -&gt; built NN with 2 branches mirroring graph; LightGBM interaction_constraints tested</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_may_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-jun-2022</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>sebastianvangerwen</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>problem-fit-NN</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>masatomurakawamm;ehekatlact</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>2106.16057;2002.08338</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>DAE-as-base-encoder</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="8" t="inlineStr"/>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>DAE-for-imputation: task IS missing-value imputation; 7-layer MLP with feature-wise mask embeddings (16-dim); masked MSE loss; conditional output (use pred only at masked positions)</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_jun_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s6e1</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>mahoganybuttstrings</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;yekenot;omidbaghchehsaraei;siukeitin;masayakawamata;mikhailnaumov</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>Ridge-as-stacker;target-encoding-stack;MLP-stacker</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P43" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;masayakawamata</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t>Strength-over-diversity inversion (vs mahog's prior diversity-no-tuning); WandB sweeps save ALL trial OOFs (190 total); Ridge + Centered Isotonic at TWO points (per-OOF + post-Ridge)</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e1_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>masayakawamata</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;tilii7;mahoganybuttstrings;optimistix</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>HC;Ridge-as-stacker;target-encoding-stack;DAE-as-base-encoder;original-as-columns</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte;tilii7</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t>Validation discipline headline: chose 0.9557801-CV submission over 0.955865 because CV-LB degraded past 0.95578; would have been 3rd if greedy; 150 OOFs + Optuna selects ~10%</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>cdeotte</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>ensemble-stacking</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>angelosmar1;azzamradman;badalkrsharma;blamerx;furqonaryadana;greysky;include4eto;johnnyhyland;lightningv08;mahoganybuttstrings;masayakawamata;mikhailnaumov;nalgirayergn;omidbaghchehsaraei;ozermehmet;rawashishsin;siukeitin;tsunamazda;yekenot;yunsuxiaozi;arunklenin</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>HC;brute-force-FE;Ridge-as-stacker;RAPIDS-XGB;target-encoding-stack;original-as-columns;pseudo-labeling;DAE-as-base-encoder</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>mahog;masayakawamata</t>
+        </is>
+      </c>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>KGMON Playbook at industrial scale: 850 candidate models from 39 public notebook ports + LLM 'AI Council' (GPT5.4+Gemini3.1+Claude4.6) generating 600K LOC; 4-level stack; snap+KDTree on IBM original</t>
+        </is>
+      </c>
+      <c r="R45" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e3_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>playground-series-s6e4</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>kirill0212 (cstdy)</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>community-template-tweak</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>wguesdon;mahoganybuttstrings;utaazu;yunsuxiaozi;include4eto;yekenot;mikhail_naumov;maria_nadeem;lucas_moraes;rohit;ashish;gnn</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr"/>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>Ridge-as-stacker;target-encoding-stack</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>mahog</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>~90% of OOFs from other Kagglers (wguesdon 30/49% + 24 others); win = meta-architecture: two-binary-classifier reframe of 3-class (Low-vs-Rest + Med-vs-High) + logit LR blend + threshold search</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e4_rank1.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Codebook" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Example (icr)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Paradigm &amp; Attribution" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Data Quality Audit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Corrections Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +44,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +69,24 @@
         <bgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE6E6"/>
+        <bgColor rgb="00FFE6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4E6"/>
+        <bgColor rgb="00FFF4E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -80,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -97,6 +117,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ46"/>
+  <dimension ref="A1:AL46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -677,6 +716,16 @@
           <t>metric</t>
         </is>
       </c>
+      <c r="AK1" s="12" t="inlineStr">
+        <is>
+          <t>top_3_margin</t>
+        </is>
+      </c>
+      <c r="AL1" s="12" t="inlineStr">
+        <is>
+          <t>distribution_shift_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -845,6 +894,14 @@
           <t>Weighted Multiclass Loss</t>
         </is>
       </c>
+      <c r="AK2" t="n">
+        <v>0.03348</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>covariate</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -979,7 +1036,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>lightgbm, catboost, xgboost, neural_network (denselight, mlp, tab_resnet, tab_transformer, autoint)</t>
+          <t>lightgbm; catboost; xgboost; denselight; mlp; tab_resnet; tab_transformer; autoint</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1013,6 +1070,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK3" t="n">
+        <v>6e-05</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1181,6 +1246,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK4" t="n">
+        <v>0.00071</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>temporal</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1347,6 +1420,14 @@
           <t>Mean Squared Log Error</t>
         </is>
       </c>
+      <c r="AK5" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1481,7 +1562,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>XGBoost, LightGBM, CatBoost, NN, Ridge, AutoML</t>
+          <t>xgboost; lightgbm; catboost; histgradientboosting; neural_network; ridge; automl</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1510,6 +1591,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK6" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>temporal</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1644,7 +1733,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>XGBoost, CatBoost, NN, Lasso, AutoGluon, Autoencoder</t>
+          <t>xgboost; catboost; neural_network; lasso; autogluon; autoencoder; keras_fm; tabm; tf_embedding_network</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1654,7 +1743,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1673,6 +1762,14 @@
           <t>Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1841,6 +1938,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK8" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1975,7 +2080,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>XGBoost; LightGBM; CatBoost; RealMLP; TabM; DANet; Resnet; LogisticRegression; RandomForest; ExtraTrees; FTTransformer; DeepFM; LNN; Trompt; Gandalf; Bartz</t>
+          <t>lightgbm; xgboost; catboost; tabm; lama-denselight; lama-dense; tabular_rnn; excelformer; modernnca; realmlp; ftt; neural_network; ann; deeptables; resnet; gandalf; saint; tabr; mlp; node; transformer; ftft; xgb_regression</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2009,6 +2114,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK9" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2177,6 +2290,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK10" t="n">
+        <v>0.00264</v>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2335,7 +2456,7 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>300000</v>
+        <v>4000000</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2345,6 +2466,14 @@
           <t>Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK11" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2479,7 +2608,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>tabm, xgboost, lightgbm, catboost, neural_network, random_forest, bart</t>
+          <t>tabm; xgboost; lightgbm; catboost; deeptables; tabr; realmlp; gandalf; grn; fttransformer; cnn; random_forest; bart</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2513,6 +2642,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK12" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2681,6 +2818,14 @@
           <t>Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK13" t="n">
+        <v>0.08758000000000001</v>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2849,6 +2994,14 @@
           <t>Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK14" t="n">
+        <v>41.07759</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3012,6 +3165,14 @@
           <t>R2 Score</t>
         </is>
       </c>
+      <c r="AK15" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3101,7 +3262,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>imputation</t>
+          <t>leave_as_is</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3180,6 +3341,14 @@
           <t>Accuracy Score</t>
         </is>
       </c>
+      <c r="AK16" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3338,6 +3507,14 @@
           <t>MAP@{K}</t>
         </is>
       </c>
+      <c r="AK17" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3501,6 +3678,14 @@
           <t>Matthews Corrcoef</t>
         </is>
       </c>
+      <c r="AK18" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3669,6 +3854,14 @@
           <t>Root Mean Squared Logarithmic Error</t>
         </is>
       </c>
+      <c r="AK19" t="n">
+        <v>0.00439</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3832,6 +4025,14 @@
           <t>Mean Columnwise Area Under Receiver Operating Characteristic Curve</t>
         </is>
       </c>
+      <c r="AK20" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3990,6 +4191,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK21" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4153,6 +4362,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK22" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4316,6 +4533,14 @@
           <t>Mean Absolute Error</t>
         </is>
       </c>
+      <c r="AK23" t="n">
+        <v>0.91931</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4474,6 +4699,14 @@
           <t>Log Loss</t>
         </is>
       </c>
+      <c r="AK24" t="n">
+        <v>0.00316</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4637,6 +4870,14 @@
           <t>Mean Absolute Error</t>
         </is>
       </c>
+      <c r="AK25" t="n">
+        <v>0.00084</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4795,6 +5036,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK26" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4958,6 +5207,14 @@
           <t>Mean Squared Log Error</t>
         </is>
       </c>
+      <c r="AK27" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5113,6 +5370,14 @@
           <t>MAP@{K}</t>
         </is>
       </c>
+      <c r="AK28" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5281,6 +5546,14 @@
           <t>Cohen Kappa Score</t>
         </is>
       </c>
+      <c r="AK29" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5449,6 +5722,14 @@
           <t>Log Loss</t>
         </is>
       </c>
+      <c r="AK30" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5612,6 +5893,14 @@
           <t>Root Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK31" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5775,6 +6064,14 @@
           <t>Root Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK32" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5936,6 +6233,14 @@
           <t>Root Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK33" t="n">
+        <v>2335.34795</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6094,6 +6399,14 @@
           <t>Root Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK34" t="n">
+        <v>0.00068</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6249,6 +6562,14 @@
           <t>Area Under Receiver Operating Characteristic Curve</t>
         </is>
       </c>
+      <c r="AK35" t="n">
+        <v>0.00277</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6412,6 +6733,14 @@
           <t>Area Under Receiver Operating Characteristic Curve</t>
         </is>
       </c>
+      <c r="AK36" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6544,7 +6873,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>catboost; xgboost; lightgbm</t>
+          <t>catboost; xgboost; lightgbm; lightgbm_goss; lightgbm_dart</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6578,6 +6907,14 @@
           <t>Accuracy Score</t>
         </is>
       </c>
+      <c r="AK37" t="n">
+        <v>0.000202</v>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6744,6 +7081,14 @@
           <t>Mean Squared Log Error</t>
         </is>
       </c>
+      <c r="AK38" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>covariate</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6753,12 +7098,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>not described</t>
+          <t>Dmitry</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>not described</t>
+          <t>Numanynklr</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6910,6 +7255,14 @@
           <t>Area Under Receiver Operating Characteristic Curve</t>
         </is>
       </c>
+      <c r="AK39" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>not-applicable</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7074,6 +7427,14 @@
           <t>Categorization Accuracy</t>
         </is>
       </c>
+      <c r="AK40" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>covariate</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7235,6 +7596,14 @@
           <t>Area Under Receiver Operating Characteristic Curve</t>
         </is>
       </c>
+      <c r="AK41" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7396,6 +7765,14 @@
           <t>Root Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK42" t="n">
+        <v>0.00047</v>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7557,6 +7934,14 @@
           <t>Root Mean Squared Error</t>
         </is>
       </c>
+      <c r="AK43" t="n">
+        <v>0.00502</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7679,7 +8064,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Quantile and equal-width binning; digit features; all features treated as categorical; within-fold target encoding (cuml TargetEncoder, 5-fold, smooth=10); genetic programming (gplearn) nonlinear features; original dataset target statistics (mean, smoothed mean, WoE, entropy) as external TE; DVAE latent representations for diversity; knowledge distillation (soft labels = 0.5 * hard labels + 0.5 * teacher RealMLP OOF)</t>
+          <t>binning; digit features; all-as-categorical; within-fold TE (cuML); gplearn nonlinear features; original-data target stats (mean/smoothed/WoE/entropy); DVAE latents</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7718,6 +8103,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK44" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7865,7 +8258,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>neural_network</t>
+          <t>gbm</t>
         </is>
       </c>
       <c r="AH45" t="n">
@@ -7879,6 +8272,14 @@
           <t>Roc Auc Score</t>
         </is>
       </c>
+      <c r="AK45" t="n">
+        <v>6.999999999999999e-05</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8038,6 +8439,14 @@
       <c r="AJ46" t="inlineStr">
         <is>
           <t>Balanced Accuracy Score</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>0.00011</v>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8543,6 +8952,86 @@
       <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Relative path to per-writeup re-evaluation doc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>--- Pass 1 audit clarifications (added 2026-05-27) ---</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>primary_model vs best_single_model vs dominant_base_model</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Three related but distinct fields: primary_model = the headline model family of the winning approach (often the family of the highest-weight contributor); best_single_model = the highest-CV single base model regardless of ensemble role; dominant_base_model = the family with the largest count of base models in the ensemble. May diverge when (a) best single is a stacker meta-learner or (b) ensemble has many of one family but the headline contributor is another. Example: s6e3 has primary=gbm, best_single=TabM, dominant_base=gbm (was incorrectly 'neural_network' until 2026-05-27 audit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>hyperparameter_tuning: automated vs optuna</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>automated = AutoML framework handles HP internally (s3e1 Kirderf with AutoGluon TabularPredictor; s3e17 ISoft with 5 AutoML frameworks). optuna = author runs explicit Optuna sweep over model HP. Edge case: s5e7 Irfan uses Optuna only for ensemble weight + threshold tuning (per-model HP hardcoded as 'optimized' dicts) — coded as 'optuna' but documented in Pass 2 winner_unique_edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>models_used (base vs stacker)</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Field captures all models that produced predictions in the pipeline, INCLUDING stacker meta-learners. NN-as-final-stacker cases (s4e9 Mart Preusse, s3e26 Hardy Xu) and CatBoost-as-final-stacker (s5e8 Mahog) list the stacker in models_used; the stacker role is captured in ensemble_method and (post-audit) in Pass 2 winner_unique_edge. Future schema could split into models_base + model_stacker for clarity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>top_3_margin</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Numeric. Absolute difference between rank-1 and rank-3 private LB scores (computed from leaderboard.json). Lower = photo-finish. Added 2026-05-27 to support photo-finish-&gt;validation-discipline coupling analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>distribution_shift_type</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Enum: temporal | covariate | label-noise | none | not-applicable. Only meaningful when distribution_shift=TRUE; otherwise 'not-applicable'. 'temporal' = time-based shift (s5e3 train years vs test years; s5e12 cutoff_id). 'covariate' = feature-distribution shift between train and test sources (s4e4 UCI vs synthetic; tps-feb-2022 mutated bacteria). 'label-noise' = same features, different label distributions. Added 2026-05-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>original_data_usage: 'none' vs 'yes' vs use-mode</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Current values mix availability with use-mode and are scheduled for split. Known issue tracked in 'Data Quality Audit' sheet as proposed-split. Until then: 'none' = neither used nor (in most cases) available; 'yes' = available and used in some unspecified way; explicit modes (concat_rows, merge_columns, both) = use mode is known. s5e10 corrected 2026-05-27 from 'yes' to 'none' (no external original).</t>
         </is>
       </c>
     </row>
@@ -12402,4 +12891,1799 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="75" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>competition_ref</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>finish_rank</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>current_value</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>issue_type</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>proposed_correction</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>source_reeval_doc</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>SCHEMA-WIDE</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr"/>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>top_3_margin</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>(does not exist)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>proposed-add</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Add numeric column: private LB spread between 1st and 3rd</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/INDEX.md</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Photo-finish margin recurs as a strategy-shaping constraint (s4e8 0.00004, s5e10 4-way tie at 0.05563, s6e2 0.00001, s5e12 0.00007). One of 6 promoted couplings (photo-finish -&gt; validation-discipline) cannot be analyzed without this column. Derivable from local leaderboard.json files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>SCHEMA-WIDE</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr"/>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>fe_techniques</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>(free text)</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>attribution-conflation</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>No Pass-1 change — Pass 2 'origination_score' + 'cited_community_members' separates 'used' from 'originated'</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/INDEX.md</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Systemic: fe_techniques captures what was used. Re-eval found ~7 entries where 'novel' techniques are credited to named community members (Sergey-s3e14, Bill Cruise-s3e3, Moonlit-s4e3, omid-s4e10, Mart Preusse-s4e9, Kirderf-s3e1, kirill0212-s6e4). Pass 2 sheet resolves cleanly; don't double-encode in Pass 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>SCHEMA-WIDE</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>distribution_shift_type</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>(does not exist; only bool distribution_shift)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>proposed-add</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Add enum: temporal / covariate / label-noise / none / not-applicable</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/INDEX.md</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Bool flags presence; loses kind. Three known cases each got different handling: s5e3 temporal-by-year (Group K Fold), s5e12 temporal-by-cutoff (post-cutoff CV), s4e4 covariate (train-on-original-no-validate). Cross-case shift-handling analysis requires this column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>SCHEMA-WIDE</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>original_data_usage</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>enum mixing availability and use mode</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>proposed-split</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Split into external_original_available (bool) + external_original_use_mode (rows-only / columns-only / both / features-derived / lookup / available-not-used / unavailable / unknown)</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/INDEX.md</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Current 'yes' / 'none' / 'concat_rows' / 'merge_columns' / 'not_described' values smush two distinct questions. cdeotte's s3e5 'available but chose not to use' (CV-driven) and s5e3 'available, used as columns' become distinguishable after the split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SCHEMA-WIDE</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>primary_model / best_single_model / dominant_base_model</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>three columns, occasionally divergent</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>codebook-only</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Add codebook entries defining what each captures and when they may diverge</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e3_rank1.md</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>s6e3 has primary_model=gbm, best_single_model=TabM, dominant_base_model=neural_network (all different) — the divergence is meaningful but the codebook doesn't define when it should occur. One paragraph of clarification, no data change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SCHEMA-WIDE</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>hyperparameter_tuning</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>none / manual / optuna / bayesian / random_search / automated / custom</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>codebook-only</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Codebook: reserve 'automated' for AutoML-handled (s3e17, s3e1); 'optuna' for explicit Optuna sweep over model HP (not ensemble weights only)</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e17_rank3.md</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>s5e7 uses Optuna only for ensemble weights + threshold (per-model HP hardcoded) but is currently coded 'optuna' same as competitions with full Optuna model-HP sweeps. The distinction matters when analyzing HP-tuning effort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>SCHEMA-WIDE</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>(semicolon list, no base/stacker distinction)</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>codebook-only</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Codebook: clarify whether stacker models are included in the list. Note: s4e9 NN-as-stacker, s3e26 NN-as-stacker, s5e8 CatBoost-as-stacker are all currently in the same list as base models.</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e9_rank1.md</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Optional schema extension: separate 'stacker_family' column. Not urgent because ensemble_method partially captures the stacker. Document the limitation in Methodology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>winner_1st</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>not described</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>missing-data</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Dmitry</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e4_rank3.md</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Actual 1st place per local leaderboard.json. Missing winner names break author-recurrence and community-graph counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>winner_2nd</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>not described</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>missing-data</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Numanynklr</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e4_rank3.md</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Actual 2nd place per local leaderboard.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>playground-series-s5e2</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>n_rows</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>inaccurate</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>4000000</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e2_rank1.md</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Combined train is train.csv (300K) + training_extra.csv (~3.7M) loaded together in cdeotte's notebook. Strategy ('single XGB w/ 500 features, no fear of overfitting') is shaped by 4M, not 300K. Misclassifies this entry in any n_rows-based analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>fe_techniques</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>...; knowledge distillation (0.5 hard + 0.5 teacher OOF); ...</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>miscategorized</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Remove 'knowledge distillation' from fe_techniques</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e2_rank1.md</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Knowledge distillation is a training-time loss/label technique, not feature engineering. Belongs in models_used or a new training-technique field, not fe_techniques. Note also: writeup §8 lists distillation under 'what did not work' for single-model gain, though it's wired into the published RealMLP notebook for ensemble diversity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s4e11</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>missing_data_strategy</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>imputation</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>inaccurate</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>leave_as_is (with per-model native handling)</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e11_rank1.md</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Author explicit in comments: 'usually best to leave the inconsistencies in the data as is.' Notebook does some imputation but the methodological principle is leave-as-is. Codebook value 'leave_as_is' may need to be added if not present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s4e7</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>lightgbm; catboost; xgboost; neural_network (lumped)</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>lumping</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Expand NN: denselight, mlp, tab_resnet, tab_transformer, autoint</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e7_rank1.md</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Cross Sellers used 5 distinct NN architectures (Denselight, MLP, Tab-Resnet, Tab-Transformer, Autoint) lumped as 'neural_network'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>original_data_usage</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>semantic-ambiguous</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>none (or 'internal-augmentation' if codebook extended)</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e10_rank1.md</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Tilii used Lasso to reverse-engineer the generator formula from training data — no external public original dataset was used. 'yes' here conflates internal-data use with external-original use. See SCHEMA-WIDE proposed split of this field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>XGBoost; CatBoost; NN; Lasso; AutoGluon; Autoencoder (6)</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>undercount</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Also: Keras FM, TabM, TF embedding networks (lumped under 'NN')</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e10_rank1.md</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>'NN' lumps multiple architectures the writeup names explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e11</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>16 families listed</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>undercount</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Add: LAMA-DenseLight, LAMA-Dense, TabulaRNN, ExcelFormer, ModernNCA (total 23)</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e11_rank1.md</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Writeup lists 23 distinct architectures; spreadsheet has 16. Affects model-family diversity counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e12</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>XGBoost; LightGBM; CatBoost; NN; Ridge; AutoML</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>undercount</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Add: HistGradientBoosting (visible in notebook MODELS list)</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e12_rank1.md</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>HistGradientBoosting visible in the published notebook's MODELS list. Also note the 'ensemble-of-ensembles' structure (Ridge stacks and prior HC outputs as candidate models inside meta-HC) isn't captured by any field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e7</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>catboost; xgboost; lightgbm (3)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>undercount</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Add: LightGBM-GOSS, LightGBM-DART (5 total)</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e7_rank2.md</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Notebook trains 5 GBDT variants; spreadsheet counts 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e7</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>hyperparameter_tuning</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>optuna</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>semantic-ambiguous</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>optuna (ensemble-weights + threshold only; per-model HP hardcoded)</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e7_rank2.md</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Optuna used only for ensemble weights + threshold tuning (cell 41); per-model params are hardcoded 'optimized' dicts with no per-model Optuna study in the notebook. Codebook should distinguish 'optuna for HP search' vs 'optuna for ensemble-weight tuning'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e8</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>tabm; xgboost; lightgbm; catboost; neural_network; random_forest; bart (7)</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>undercount</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Expand to 13: also DeepTables, TabR, RealMLP, Gandalf, GRN, FTTransformer, CNN</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e8_rank2.md</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>'neural_network' lumps 7 distinct architectures. Affects NN-architecture-diversity analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s5e8</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ensemble_method</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>undercount</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>stacking (CatBoost chosen after head-to-head test of Ridge/LGB/CatB/HC)</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e8_rank2.md</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Mahog explicitly tested 4 stacker families with reported CV/Public LB/Private LB. The chosen CatBoost stacker is a counter-example to the linear-stacker-is-universal pattern. Single 'stacking' value loses the methodologically-interesting head-to-head test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>dominant_base_model</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>inaccurate</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e3_rank1.md</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Writeup count: 90 trees vs 60 NNs — trees dominate by count. NN label likely because best_single_model is TabM. With three columns capturing slightly different things (primary_model / best_single_model / dominant_base_model), codebook should clarify when each may diverge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>playground-series-s4e10</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>best_single_model</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>not_described</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>missing-data</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>(inferable from notebook; author didn't enumerate per-model CV in writeup)</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e10_rank2.md</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>Honest 'not_described' is defensible — writeup doesn't enumerate per-model CV scores. Notebook has all 9 base-model CVs computed; could be inferred if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>playground-series-s6e4</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>(own-model count)</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>6 own models (writeup)</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>semantic-ambiguous</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>7 visible in notebook (my_rmlp_xgb_2 is a blend)</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e4_rank1.md</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>Writeup says 6 own models; notebook cell 24 shows 7 after exclusions. The discrepancy is one entry being a blend rather than a clean own-model. Not a spreadsheet field per se; flagged for completeness.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>competition_ref</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>finish_rank</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>old_value</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>new_value</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>winner_1st</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>not described</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Dmitry</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Actual 1st place per leaderboard.json. Was 'not described'.</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>data/raw/playground-series-s3e4/leaderboard.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>winner_2nd</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>not described</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Numanynklr</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Actual 2nd place per leaderboard.json. Was 'not described'.</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>data/raw/playground-series-s3e4/leaderboard.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>playground-series-s5e2</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>n_rows</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>4000000</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Combined train.csv (300K) + training_extra.csv (~3.7M) loaded together in cdeotte's notebook. Strategy was shaped by 4M, not 300K.</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>fe_techniques</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Quantile and equal-width binning; digit features; all features treated as categorical; within-fold target encoding (cuml TargetEncoder, 5-fold, smooth=10); genetic programming (gplearn) nonlinear features; original dataset target statistics (mean, smoothed mean, WoE, entropy) as external TE; DVAE latent representations for diversity; knowledge distillation (soft labels = 0.5 * hard labels + 0.5 * teacher RealMLP OOF)</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>binning; digit features; all-as-categorical; within-fold TE (cuML); gplearn nonlinear features; original-data target stats (mean/smoothed/WoE/entropy); DVAE latents</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Removed 'knowledge distillation (0.5 hard + 0.5 teacher OOF)' — training-time technique, not FE.</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e11</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>missing_data_strategy</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>imputation</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>leave_as_is</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Author principle (explicit in comments): 'usually best to leave the inconsistencies in the data as is'. Was 'imputation'.</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e7</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>lightgbm, catboost, xgboost, neural_network (denselight, mlp, tab_resnet, tab_transformer, autoint)</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>lightgbm; catboost; xgboost; denselight; mlp; tab_resnet; tab_transformer; autoint</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Cross Sellers used 5 distinct NN architectures (Denselight, MLP, Tab-Resnet, Tab-Transformer, Autoint) previously lumped as 'neural_network'.</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e7_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>original_data_usage</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Tilii used Lasso to reverse-engineer generator formula from training data. No external public original dataset was used. Was 'yes' which conflated internal-data use with external-original use.</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>XGBoost, CatBoost, NN, Lasso, AutoGluon, Autoencoder</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>xgboost; catboost; neural_network; lasso; autogluon; autoencoder; keras_fm; tabm; tf_embedding_network</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Writeup also names Keras FM, TabM, TF embedding networks (previously lumped under 'NN').</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e11</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>XGBoost; LightGBM; CatBoost; RealMLP; TabM; DANet; Resnet; LogisticRegression; RandomForest; ExtraTrees; FTTransformer; DeepFM; LNN; Trompt; Gandalf; Bartz</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>lightgbm; xgboost; catboost; tabm; lama-denselight; lama-dense; tabular_rnn; excelformer; modernnca; realmlp; ftt; neural_network; ann; deeptables; resnet; gandalf; saint; tabr; mlp; node; transformer; ftft; xgb_regression</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Writeup lists 23 distinct architectures; spreadsheet previously had 16. Added: LAMA-DenseLight, LAMA-Dense, TabulaRNN, ExcelFormer, ModernNCA, plus distinguished XGB-regression and LightGBM-DART variants.</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e12</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>XGBoost, LightGBM, CatBoost, NN, Ridge, AutoML</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>xgboost; lightgbm; catboost; histgradientboosting; neural_network; ridge; automl</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Added HistGradientBoosting (visible in notebook MODELS list).</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e12_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e7</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>catboost; xgboost; lightgbm</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>catboost; xgboost; lightgbm; lightgbm_goss; lightgbm_dart</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Notebook trains 5 GBDT variants; previously counted 3.</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e7_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e8</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>models_used</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>tabm, xgboost, lightgbm, catboost, neural_network, random_forest, bart</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>tabm; xgboost; lightgbm; catboost; deeptables; tabr; realmlp; gandalf; grn; fttransformer; cnn; random_forest; bart</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Writeup shows 13 distinct architectures. Previous lumped under 'neural_network' (7 categories total). Now distinguishes DeepTables, TabR, RealMLP, Gandalf, GRN, FTTransformer, CNN.</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e8_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>dominant_base_model</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>neural_network</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>gbm</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Writeup count: 90 trees vs 60 NNs — trees dominate by count. Previous 'neural_network' label likely came from best_single_model being TabM.</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e3_rank1.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/kaggle_meta_analysis.xlsx
+++ b/data/kaggle_meta_analysis.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL46"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -726,6 +726,16 @@
           <t>distribution_shift_type</t>
         </is>
       </c>
+      <c r="AM1" s="12" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="AN1" s="12" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -902,6 +912,16 @@
           <t>covariate</t>
         </is>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1078,6 +1098,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1254,6 +1284,16 @@
           <t>temporal</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1428,6 +1468,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1599,6 +1649,16 @@
           <t>temporal</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1770,6 +1830,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1946,6 +2016,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2122,6 +2202,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2298,6 +2388,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2474,6 +2574,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>columns-only</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2650,6 +2760,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2826,6 +2946,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3002,6 +3132,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3173,6 +3313,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>available-not-used</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3349,6 +3499,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3515,6 +3675,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3686,6 +3856,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3862,6 +4042,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4033,6 +4223,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4199,6 +4399,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4370,6 +4580,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4541,6 +4761,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4707,6 +4937,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4878,6 +5118,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5044,6 +5294,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5215,6 +5475,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5378,6 +5648,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5554,6 +5834,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>available-not-used</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5730,6 +6020,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5901,6 +6201,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6072,6 +6382,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6241,6 +6561,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6407,6 +6737,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6570,6 +6910,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6741,6 +7091,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6915,6 +7275,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7089,6 +7459,16 @@
           <t>covariate</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7263,6 +7643,16 @@
           <t>not-applicable</t>
         </is>
       </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7435,6 +7825,16 @@
           <t>covariate</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7604,6 +8004,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7773,6 +8183,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7942,6 +8362,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8111,6 +8541,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8280,6 +8720,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8447,6 +8897,16 @@
       <c r="AL46" t="inlineStr">
         <is>
           <t>none</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>rows-only</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -9032,6 +9492,50 @@
       <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Current values mix availability with use-mode and are scheduled for split. Known issue tracked in 'Data Quality Audit' sheet as proposed-split. Until then: 'none' = neither used nor (in most cases) available; 'yes' = available and used in some unspecified way; explicit modes (concat_rows, merge_columns, both) = use mode is known. s5e10 corrected 2026-05-27 from 'yes' to 'none' (no external original).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>--- Pass 1 split (added 2026-05-27): original_data_usage ---</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>original_data_usage (DEPRECATED)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>DEPRECATED 2026-05-27. Conflated availability and use mode. Use external_original_available + external_original_use_mode instead. Old values retained for audit trail; new analyses should reference the new columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>TRUE | FALSE | unknown. TRUE if a public external original dataset exists for this competition (regardless of whether the winner used it). 'unknown' when writeup is silent on this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>rows-only | columns-only | both | features-derived | lookup | available-not-used | unavailable | unknown. How the external original is used: rows-only = concatenated as training rows; columns-only = original-as-columns (cdeotte's merge_columns); both = concat + columns; features-derived = aggregated stats from original used as features (e.g. target-mean TE on original); lookup = direct test-to-original key-match or KDTree (the lookup-exploit family); available-not-used = original exists but author deliberately did not use (cv-driven decision); unavailable = no external original exists; unknown = writeup silent.</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14683,6 +15187,3696 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>icr-identify-age-related-conditions</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split.</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/icr_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>icr-identify-age-related-conditions</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split.</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/icr_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e7</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original + target reversal trick on duplicates.</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e7_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e7</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original + target reversal trick on duplicates.</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e7_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e3</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr"/>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. cdeotte's deliberate dual-mode use (rows for XGB+TabPFN, columns for SVC).</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e3_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e3</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr"/>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. cdeotte's deliberate dual-mode use (rows for XGB+TabPFN, columns for SVC).</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e3_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e5</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr"/>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Minimally used (concat only); not column-exploited.</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e5</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Minimally used (concat only); not column-exploited.</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e12</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr"/>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Orig_as_columns base model + concat for others.</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e12_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e12</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Orig_as_columns base model + concat for others.</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e12_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr"/>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No external original; Lasso reverse-engineered the generator formula from training data (corrected from 'yes' on 2026-05-27).</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e10</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr"/>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No external original; Lasso reverse-engineered the generator formula from training data (corrected from 'yes' on 2026-05-27).</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e10</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr"/>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat_rows.</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e10_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e10</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr"/>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat_rows.</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e10_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e11</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr"/>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public loan dataset concatenated for training rows.</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e11</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr"/>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public loan dataset concatenated for training rows.</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e1</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr"/>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public bank-churn dataset; CatBoost-encoder-order-sensitivity discovery.</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e1_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e1</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public bank-churn dataset; CatBoost-encoder-order-sensitivity discovery.</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e1_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e2</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr"/>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. cdeotte 'manufacture suggested retail price' columns-only feature.</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e2</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr"/>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>columns-only</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. cdeotte 'manufacture suggested retail price' columns-only feature.</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e8</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr"/>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Concat + TE on bigrams using BOTH competition + original targets.</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e8_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e8</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr"/>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Concat + TE on bigrams using BOTH competition + original targets.</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e8_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e4</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr"/>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Writeup doesn't explicitly cite external original use.</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e4_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e4</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr"/>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Writeup doesn't explicitly cite external original use.</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e4_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e9</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr"/>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original car-price dataset concat.</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e9_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e9</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr"/>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original car-price dataset concat.</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e9_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e5</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr"/>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Original existed but 'completely different from train dataset' — author used for EDA only.</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e5</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>available-not-used</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Original existed but 'completely different from train dataset' — author used for EDA only.</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e11</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr"/>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat.</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e11</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat.</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e6</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr"/>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Dual-mode: concat_rows for some models + columns (TE against original) for the 2268-feature monster.</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e6_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e6</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr"/>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Dual-mode: concat_rows for some models + columns (TE against original) for the 2268-feature monster.</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e6_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e8</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr"/>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Concat + siukeitin's 'exact solution to original' feature (features-derived from original target).</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e8_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e8</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr"/>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Concat + siukeitin's 'exact solution to original' feature (features-derived from original target).</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e8_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e12</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr"/>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. First cdeotte writeup without public original.</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e12_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e12</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr"/>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. First cdeotte writeup without public original.</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e12_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e3</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr"/>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public UCI steel-plates dataset concat.</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e3_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e3</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public UCI steel-plates dataset concat.</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e3_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e24</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr"/>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat.</t>
+        </is>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e24_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e24</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat.</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e24_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e23</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr"/>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e23_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e23</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e23_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e14</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr"/>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Lookup exploit: match test rows to original by (fruitset, fruitmass) keys; primary winning mechanism.</t>
+        </is>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e14_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e14</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Lookup exploit: match test rows to original by (fruitset, fruitmass) keys; primary winning mechanism.</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e14_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e26</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr"/>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Author didn't disclose external-original use; not_described in Pass 1.</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e26_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e26</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Author didn't disclose external-original use; not_described in Pass 1.</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e26_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e16</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr"/>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat + generator-driven additional synthetic data.</t>
+        </is>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e16_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e16</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat + generator-driven additional synthetic data.</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e16_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e17</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr"/>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Writeup minimal (~30 lines); external-original use not described.</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e17_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e17</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Writeup minimal (~30 lines); external-original use not described.</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e17_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e11</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr"/>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original media-campaign dataset concat.</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e11</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original media-campaign dataset concat.</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e11_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e13</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr"/>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e13_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e13</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e13_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e5</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr"/>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Original existed but author chose NOT to use (overfit local CV).</t>
+        </is>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e5</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>available-not-used</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Original existed but author chose NOT to use (overfit local CV).</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e5_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e10</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr"/>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e10</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e10_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e9</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr"/>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e9_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e9</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr"/>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original used.</t>
+        </is>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e9_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e8</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr"/>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public gemstone dataset concat; lookup-exploit TESTED but rejected (overfit public LB).</t>
+        </is>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e8_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e8</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public gemstone dataset concat; lookup-exploit TESTED but rejected (overfit public LB).</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e8_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e6</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr"/>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public Paris housing dataset concat.</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e6_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e6</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public Paris housing dataset concat.</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e6_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e1</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr"/>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public California Housing dataset concat.</t>
+        </is>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e1_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e1</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr"/>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public California Housing dataset concat.</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e1_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e7</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr"/>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat + adversarial-validation filter; inversion-lookup exploit.</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e7_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e7</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr"/>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public original concat + adversarial-validation filter; inversion-lookup exploit.</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e7_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e3</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr"/>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public IBM HR dataset concat.</t>
+        </is>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e3_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e3</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr"/>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public IBM HR dataset concat.</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e3_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e7</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr"/>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. match_p trick: exact-row-join with public original on 7-feature tuple.</t>
+        </is>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e7_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s5e7</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr"/>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. match_p trick: exact-row-join with public original on 7-feature tuple.</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s5e7_rank2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e4</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr"/>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public UCI Abalone dataset; train-on-original-only-no-validate scheme for distribution-shift handling.</t>
+        </is>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e4_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s4e4</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public UCI Abalone dataset; train-on-original-only-no-validate scheme for distribution-shift handling.</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s4e4_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr"/>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No external original used (PCA-anonymized features make exploit-original infeasible).</t>
+        </is>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e4_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s3e4</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr"/>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No external original used (PCA-anonymized features make exploit-original infeasible).</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s3e4_rank3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-feb-2022</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr"/>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G91" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original; exploit was source-code-level reverse-engineering of np.random.</t>
+        </is>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_feb_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-feb-2022</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original; exploit was source-code-level reverse-engineering of np.random.</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_feb_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-may-2022</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr"/>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original.</t>
+        </is>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_may_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-may-2022</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr"/>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original.</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_may_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-jun-2022</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr"/>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G95" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original.</t>
+        </is>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_jun_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-jun-2022</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr"/>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G96" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No public original.</t>
+        </is>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/tps_jun_2022_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e1</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr"/>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G97" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No external dataset used; first of s6 quartet without one.</t>
+        </is>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e1_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e1</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr"/>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>unavailable</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. No external dataset used; first of s6 quartet without one.</t>
+        </is>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e1_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr"/>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public heart-disease original + target stats (mean/smoothed/WoE/entropy) as external TE features.</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr"/>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H100" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. Public heart-disease original + target stats (mean/smoothed/WoE/entropy) as external TE features.</t>
+        </is>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e2_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr"/>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. IBM Telco Customer Churn (7,032 rows) + snap features + cKDTree nearest-neighbor lookup + PCA/GRP projection fitted on original.</t>
+        </is>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e3_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B102" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr"/>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. IBM Telco Customer Churn (7,032 rows) + snap features + cKDTree nearest-neighbor lookup + PCA/GRP projection fitted on original.</t>
+        </is>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e3_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e4</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>external_original_available</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="inlineStr"/>
+      <c r="F103" s="15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H103" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. External miadul/irrigation-water-requirement-prediction-dataset concatenated.</t>
+        </is>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e4_rank1.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>playground-series-s6e4</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>external_original_use_mode</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr"/>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>rows-only</t>
+        </is>
+      </c>
+      <c r="G104" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>Backfilled from original_data_usage split. External miadul/irrigation-water-requirement-prediction-dataset concatenated.</t>
+        </is>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>analysis/writeup-reevaluation/s6e4_rank1.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
